--- a/data/test_financial_data.xlsx
+++ b/data/test_financial_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vincentgiang/Documents/GitHub/my-finance-hub/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE2C58A5-3D61-8843-B32D-1144D857827D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57942D9F-986A-1944-87A3-913D64A5DFF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21260" activeTab="1" xr2:uid="{3BD675DF-4CB5-DF44-965C-9C90F624AC09}"/>
   </bookViews>
